--- a/Data/TegulaCharacteristicsList.xlsx
+++ b/Data/TegulaCharacteristicsList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nathaniel Morley\Documents\Research\TegulaApertureMorph\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nathaniel Morley\Documents\GitHub\teg-aperture-morph\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAF13C24-E492-40C9-85B8-E1298A4E99FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A126CBF0-E1FB-46A3-A33C-0E273CC8C7AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="161">
   <si>
     <t>Location</t>
   </si>
@@ -365,16 +365,160 @@
     <t>S50</t>
   </si>
   <si>
-    <t>Prasiola:</t>
-  </si>
-  <si>
-    <t>Stawberry</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>SD</t>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>Mathers</t>
+  </si>
+  <si>
+    <t>Moderate</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t>M6</t>
+  </si>
+  <si>
+    <t>M7</t>
+  </si>
+  <si>
+    <t>M8</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>M10</t>
+  </si>
+  <si>
+    <t>M11</t>
+  </si>
+  <si>
+    <t>M12</t>
+  </si>
+  <si>
+    <t>M13</t>
+  </si>
+  <si>
+    <t>M14</t>
+  </si>
+  <si>
+    <t>M15</t>
+  </si>
+  <si>
+    <t>M16</t>
+  </si>
+  <si>
+    <t>M17</t>
+  </si>
+  <si>
+    <t>M18</t>
+  </si>
+  <si>
+    <t>M19</t>
+  </si>
+  <si>
+    <t>M20</t>
+  </si>
+  <si>
+    <t>M21</t>
+  </si>
+  <si>
+    <t>M22</t>
+  </si>
+  <si>
+    <t>M23</t>
+  </si>
+  <si>
+    <t>M24</t>
+  </si>
+  <si>
+    <t>M25</t>
+  </si>
+  <si>
+    <t>M26</t>
+  </si>
+  <si>
+    <t>M27</t>
+  </si>
+  <si>
+    <t>M28</t>
+  </si>
+  <si>
+    <t>M29</t>
+  </si>
+  <si>
+    <t>M30</t>
+  </si>
+  <si>
+    <t>M31</t>
+  </si>
+  <si>
+    <t>M32</t>
+  </si>
+  <si>
+    <t>M33</t>
+  </si>
+  <si>
+    <t>M34</t>
+  </si>
+  <si>
+    <t>M35</t>
+  </si>
+  <si>
+    <t>M36</t>
+  </si>
+  <si>
+    <t>M37</t>
+  </si>
+  <si>
+    <t>M38</t>
+  </si>
+  <si>
+    <t>M39</t>
+  </si>
+  <si>
+    <t>M40</t>
+  </si>
+  <si>
+    <t>M41</t>
+  </si>
+  <si>
+    <t>M42</t>
+  </si>
+  <si>
+    <t>M43</t>
+  </si>
+  <si>
+    <t>M44</t>
+  </si>
+  <si>
+    <t>M45</t>
+  </si>
+  <si>
+    <t>M46</t>
+  </si>
+  <si>
+    <t>M47</t>
+  </si>
+  <si>
+    <t>M48</t>
+  </si>
+  <si>
+    <t>M49</t>
+  </si>
+  <si>
+    <t>M50</t>
   </si>
 </sst>
 </file>
@@ -707,7 +851,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:E151"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
@@ -717,7 +861,7 @@
     <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -734,7 +878,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -751,7 +895,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -768,7 +912,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -785,7 +929,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -801,14 +945,8 @@
       <c r="E5">
         <v>23.3</v>
       </c>
-      <c r="J5" t="s">
-        <v>111</v>
-      </c>
-      <c r="K5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -824,19 +962,8 @@
       <c r="E6">
         <v>25.8</v>
       </c>
-      <c r="I6" t="s">
-        <v>109</v>
-      </c>
-      <c r="J6">
-        <f>AVERAGE(E2:E51)</f>
-        <v>21.679999999999996</v>
-      </c>
-      <c r="K6">
-        <f>_xlfn.STDEV.S(E2:E51)</f>
-        <v>3.5368612858157404</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -852,19 +979,8 @@
       <c r="E7">
         <v>22.9</v>
       </c>
-      <c r="I7" t="s">
-        <v>110</v>
-      </c>
-      <c r="J7">
-        <f>AVERAGE(E52:E101)</f>
-        <v>18.437999999999992</v>
-      </c>
-      <c r="K7">
-        <f>_xlfn.STDEV.S(E52:E101)</f>
-        <v>3.3879070656844532</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -881,7 +997,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -898,7 +1014,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -915,7 +1031,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -932,7 +1048,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -949,7 +1065,7 @@
         <v>30.8</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -966,7 +1082,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -983,7 +1099,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -1000,7 +1116,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -2460,6 +2576,856 @@
       </c>
       <c r="E101">
         <v>22.3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>109</v>
+      </c>
+      <c r="B102" t="s">
+        <v>111</v>
+      </c>
+      <c r="C102" t="s">
+        <v>112</v>
+      </c>
+      <c r="D102">
+        <v>1</v>
+      </c>
+      <c r="E102">
+        <v>19.600000000000001</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>110</v>
+      </c>
+      <c r="B103" t="s">
+        <v>111</v>
+      </c>
+      <c r="C103" t="s">
+        <v>112</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="E103">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>113</v>
+      </c>
+      <c r="B104" t="s">
+        <v>111</v>
+      </c>
+      <c r="C104" t="s">
+        <v>112</v>
+      </c>
+      <c r="D104">
+        <v>1</v>
+      </c>
+      <c r="E104">
+        <v>17.600000000000001</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>114</v>
+      </c>
+      <c r="B105" t="s">
+        <v>111</v>
+      </c>
+      <c r="C105" t="s">
+        <v>112</v>
+      </c>
+      <c r="D105">
+        <v>1</v>
+      </c>
+      <c r="E105">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>115</v>
+      </c>
+      <c r="B106" t="s">
+        <v>111</v>
+      </c>
+      <c r="C106" t="s">
+        <v>112</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
+      </c>
+      <c r="E106">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>116</v>
+      </c>
+      <c r="B107" t="s">
+        <v>111</v>
+      </c>
+      <c r="C107" t="s">
+        <v>112</v>
+      </c>
+      <c r="D107">
+        <v>1</v>
+      </c>
+      <c r="E107">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>117</v>
+      </c>
+      <c r="B108" t="s">
+        <v>111</v>
+      </c>
+      <c r="C108" t="s">
+        <v>112</v>
+      </c>
+      <c r="D108">
+        <v>0</v>
+      </c>
+      <c r="E108">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>118</v>
+      </c>
+      <c r="B109" t="s">
+        <v>111</v>
+      </c>
+      <c r="C109" t="s">
+        <v>112</v>
+      </c>
+      <c r="D109">
+        <v>0</v>
+      </c>
+      <c r="E109">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>119</v>
+      </c>
+      <c r="B110" t="s">
+        <v>111</v>
+      </c>
+      <c r="C110" t="s">
+        <v>112</v>
+      </c>
+      <c r="D110">
+        <v>1</v>
+      </c>
+      <c r="E110">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>120</v>
+      </c>
+      <c r="B111" t="s">
+        <v>111</v>
+      </c>
+      <c r="C111" t="s">
+        <v>112</v>
+      </c>
+      <c r="D111">
+        <v>1</v>
+      </c>
+      <c r="E111">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>121</v>
+      </c>
+      <c r="B112" t="s">
+        <v>111</v>
+      </c>
+      <c r="C112" t="s">
+        <v>112</v>
+      </c>
+      <c r="D112">
+        <v>0</v>
+      </c>
+      <c r="E112">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>122</v>
+      </c>
+      <c r="B113" t="s">
+        <v>111</v>
+      </c>
+      <c r="C113" t="s">
+        <v>112</v>
+      </c>
+      <c r="D113">
+        <v>0</v>
+      </c>
+      <c r="E113">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>123</v>
+      </c>
+      <c r="B114" t="s">
+        <v>111</v>
+      </c>
+      <c r="C114" t="s">
+        <v>112</v>
+      </c>
+      <c r="D114">
+        <v>1</v>
+      </c>
+      <c r="E114">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>124</v>
+      </c>
+      <c r="B115" t="s">
+        <v>111</v>
+      </c>
+      <c r="C115" t="s">
+        <v>112</v>
+      </c>
+      <c r="D115">
+        <v>0</v>
+      </c>
+      <c r="E115">
+        <v>18.399999999999999</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>125</v>
+      </c>
+      <c r="B116" t="s">
+        <v>111</v>
+      </c>
+      <c r="C116" t="s">
+        <v>112</v>
+      </c>
+      <c r="D116">
+        <v>0</v>
+      </c>
+      <c r="E116">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>126</v>
+      </c>
+      <c r="B117" t="s">
+        <v>111</v>
+      </c>
+      <c r="C117" t="s">
+        <v>112</v>
+      </c>
+      <c r="D117">
+        <v>1</v>
+      </c>
+      <c r="E117">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>127</v>
+      </c>
+      <c r="B118" t="s">
+        <v>111</v>
+      </c>
+      <c r="C118" t="s">
+        <v>112</v>
+      </c>
+      <c r="D118">
+        <v>1</v>
+      </c>
+      <c r="E118">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>128</v>
+      </c>
+      <c r="B119" t="s">
+        <v>111</v>
+      </c>
+      <c r="C119" t="s">
+        <v>112</v>
+      </c>
+      <c r="D119">
+        <v>0</v>
+      </c>
+      <c r="E119">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>129</v>
+      </c>
+      <c r="B120" t="s">
+        <v>111</v>
+      </c>
+      <c r="C120" t="s">
+        <v>112</v>
+      </c>
+      <c r="D120">
+        <v>1</v>
+      </c>
+      <c r="E120">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>130</v>
+      </c>
+      <c r="B121" t="s">
+        <v>111</v>
+      </c>
+      <c r="C121" t="s">
+        <v>112</v>
+      </c>
+      <c r="D121">
+        <v>0</v>
+      </c>
+      <c r="E121">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>131</v>
+      </c>
+      <c r="B122" t="s">
+        <v>111</v>
+      </c>
+      <c r="C122" t="s">
+        <v>112</v>
+      </c>
+      <c r="D122">
+        <v>1</v>
+      </c>
+      <c r="E122">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>132</v>
+      </c>
+      <c r="B123" t="s">
+        <v>111</v>
+      </c>
+      <c r="C123" t="s">
+        <v>112</v>
+      </c>
+      <c r="D123">
+        <v>1</v>
+      </c>
+      <c r="E123">
+        <v>18.399999999999999</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>133</v>
+      </c>
+      <c r="B124" t="s">
+        <v>111</v>
+      </c>
+      <c r="C124" t="s">
+        <v>112</v>
+      </c>
+      <c r="D124">
+        <v>1</v>
+      </c>
+      <c r="E124">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>134</v>
+      </c>
+      <c r="B125" t="s">
+        <v>111</v>
+      </c>
+      <c r="C125" t="s">
+        <v>112</v>
+      </c>
+      <c r="D125">
+        <v>0</v>
+      </c>
+      <c r="E125">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>135</v>
+      </c>
+      <c r="B126" t="s">
+        <v>111</v>
+      </c>
+      <c r="C126" t="s">
+        <v>112</v>
+      </c>
+      <c r="D126">
+        <v>1</v>
+      </c>
+      <c r="E126">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>136</v>
+      </c>
+      <c r="B127" t="s">
+        <v>111</v>
+      </c>
+      <c r="C127" t="s">
+        <v>112</v>
+      </c>
+      <c r="D127">
+        <v>1</v>
+      </c>
+      <c r="E127">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>137</v>
+      </c>
+      <c r="B128" t="s">
+        <v>111</v>
+      </c>
+      <c r="C128" t="s">
+        <v>112</v>
+      </c>
+      <c r="D128">
+        <v>1</v>
+      </c>
+      <c r="E128">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>138</v>
+      </c>
+      <c r="B129" t="s">
+        <v>111</v>
+      </c>
+      <c r="C129" t="s">
+        <v>112</v>
+      </c>
+      <c r="D129">
+        <v>0</v>
+      </c>
+      <c r="E129">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>139</v>
+      </c>
+      <c r="B130" t="s">
+        <v>111</v>
+      </c>
+      <c r="C130" t="s">
+        <v>112</v>
+      </c>
+      <c r="D130">
+        <v>0</v>
+      </c>
+      <c r="E130">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>140</v>
+      </c>
+      <c r="B131" t="s">
+        <v>111</v>
+      </c>
+      <c r="C131" t="s">
+        <v>112</v>
+      </c>
+      <c r="D131">
+        <v>1</v>
+      </c>
+      <c r="E131">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>141</v>
+      </c>
+      <c r="B132" t="s">
+        <v>111</v>
+      </c>
+      <c r="C132" t="s">
+        <v>112</v>
+      </c>
+      <c r="D132">
+        <v>1</v>
+      </c>
+      <c r="E132">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>142</v>
+      </c>
+      <c r="B133" t="s">
+        <v>111</v>
+      </c>
+      <c r="C133" t="s">
+        <v>112</v>
+      </c>
+      <c r="D133">
+        <v>0</v>
+      </c>
+      <c r="E133">
+        <v>17.899999999999999</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>143</v>
+      </c>
+      <c r="B134" t="s">
+        <v>111</v>
+      </c>
+      <c r="C134" t="s">
+        <v>112</v>
+      </c>
+      <c r="D134">
+        <v>1</v>
+      </c>
+      <c r="E134">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>144</v>
+      </c>
+      <c r="B135" t="s">
+        <v>111</v>
+      </c>
+      <c r="C135" t="s">
+        <v>112</v>
+      </c>
+      <c r="D135">
+        <v>0</v>
+      </c>
+      <c r="E135">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>145</v>
+      </c>
+      <c r="B136" t="s">
+        <v>111</v>
+      </c>
+      <c r="C136" t="s">
+        <v>112</v>
+      </c>
+      <c r="D136">
+        <v>1</v>
+      </c>
+      <c r="E136">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>146</v>
+      </c>
+      <c r="B137" t="s">
+        <v>111</v>
+      </c>
+      <c r="C137" t="s">
+        <v>112</v>
+      </c>
+      <c r="D137">
+        <v>1</v>
+      </c>
+      <c r="E137">
+        <v>18.100000000000001</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>147</v>
+      </c>
+      <c r="B138" t="s">
+        <v>111</v>
+      </c>
+      <c r="C138" t="s">
+        <v>112</v>
+      </c>
+      <c r="D138">
+        <v>1</v>
+      </c>
+      <c r="E138">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>148</v>
+      </c>
+      <c r="B139" t="s">
+        <v>111</v>
+      </c>
+      <c r="C139" t="s">
+        <v>112</v>
+      </c>
+      <c r="D139">
+        <v>1</v>
+      </c>
+      <c r="E139">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>149</v>
+      </c>
+      <c r="B140" t="s">
+        <v>111</v>
+      </c>
+      <c r="C140" t="s">
+        <v>112</v>
+      </c>
+      <c r="D140">
+        <v>1</v>
+      </c>
+      <c r="E140">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>150</v>
+      </c>
+      <c r="B141" t="s">
+        <v>111</v>
+      </c>
+      <c r="C141" t="s">
+        <v>112</v>
+      </c>
+      <c r="D141">
+        <v>1</v>
+      </c>
+      <c r="E141">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>151</v>
+      </c>
+      <c r="B142" t="s">
+        <v>111</v>
+      </c>
+      <c r="C142" t="s">
+        <v>112</v>
+      </c>
+      <c r="D142">
+        <v>0</v>
+      </c>
+      <c r="E142">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>152</v>
+      </c>
+      <c r="B143" t="s">
+        <v>111</v>
+      </c>
+      <c r="C143" t="s">
+        <v>112</v>
+      </c>
+      <c r="D143">
+        <v>0</v>
+      </c>
+      <c r="E143">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>153</v>
+      </c>
+      <c r="B144" t="s">
+        <v>111</v>
+      </c>
+      <c r="C144" t="s">
+        <v>112</v>
+      </c>
+      <c r="D144">
+        <v>1</v>
+      </c>
+      <c r="E144">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>154</v>
+      </c>
+      <c r="B145" t="s">
+        <v>111</v>
+      </c>
+      <c r="C145" t="s">
+        <v>112</v>
+      </c>
+      <c r="D145">
+        <v>0</v>
+      </c>
+      <c r="E145">
+        <v>18.100000000000001</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>155</v>
+      </c>
+      <c r="B146" t="s">
+        <v>111</v>
+      </c>
+      <c r="C146" t="s">
+        <v>112</v>
+      </c>
+      <c r="D146">
+        <v>1</v>
+      </c>
+      <c r="E146">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>156</v>
+      </c>
+      <c r="B147" t="s">
+        <v>111</v>
+      </c>
+      <c r="C147" t="s">
+        <v>112</v>
+      </c>
+      <c r="D147">
+        <v>1</v>
+      </c>
+      <c r="E147">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>157</v>
+      </c>
+      <c r="B148" t="s">
+        <v>111</v>
+      </c>
+      <c r="C148" t="s">
+        <v>112</v>
+      </c>
+      <c r="D148">
+        <v>1</v>
+      </c>
+      <c r="E148">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>158</v>
+      </c>
+      <c r="B149" t="s">
+        <v>111</v>
+      </c>
+      <c r="C149" t="s">
+        <v>112</v>
+      </c>
+      <c r="D149">
+        <v>1</v>
+      </c>
+      <c r="E149">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>159</v>
+      </c>
+      <c r="B150" t="s">
+        <v>111</v>
+      </c>
+      <c r="C150" t="s">
+        <v>112</v>
+      </c>
+      <c r="D150">
+        <v>0</v>
+      </c>
+      <c r="E150">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>160</v>
+      </c>
+      <c r="B151" t="s">
+        <v>111</v>
+      </c>
+      <c r="C151" t="s">
+        <v>112</v>
+      </c>
+      <c r="D151">
+        <v>1</v>
+      </c>
+      <c r="E151">
+        <v>17.5</v>
       </c>
     </row>
   </sheetData>
